--- a/frontend/web-dashboard/public/templates/MERCON_Vehicles_Import_Template.xlsx
+++ b/frontend/web-dashboard/public/templates/MERCON_Vehicles_Import_Template.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📌 Guide &amp; Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🚛 Vehicles &amp; Trailers Directory" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🚛 Vehicles &amp; Trailers" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -606,7 +606,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="85" customWidth="1" min="2" max="2"/>
@@ -758,7 +758,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I60"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
